--- a/www/download/COUNTRY.ITA.rpA2.xlsx
+++ b/www/download/COUNTRY.ITA.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Itália</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>0.840781231385862</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.586</t>
+          <t>0.796666774552586</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.554</t>
+          <t>0.878518444762489</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.895479663178239</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.938262380506083</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>1.08271976951272</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>1.11656987056528</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.535</t>
+          <t>1.05752963977825</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.884017009933639</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>0.803923184260651</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>0.803793929556715</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>0.796432001820435</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>0.729660730035597</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902071681034</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948696375644</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>21.841</t>
+          <t>1.91075421840343</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21.966</t>
+          <t>1.82653301324318</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.035</t>
+          <t>2.02415789515354</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.253</t>
+          <t>2.00745118255007</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22.494</t>
+          <t>1.95977783411466</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>1.82291638900841</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>23.393</t>
+          <t>1.85874208836858</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>23.793</t>
+          <t>1.81423210345589</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>24.15</t>
+          <t>1.7098901389645</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24.256</t>
+          <t>1.43455145026292</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>24.396</t>
+          <t>1.51992487280099</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>24.874</t>
+          <t>1.53912226310644</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>25.188</t>
+          <t>1.76317261778737</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>25.278</t>
+          <t>1.96604103278814</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>25.079</t>
+          <t>2.15653422778019</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15.959</t>
+          <t>1.08610973969103</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16.051</t>
+          <t>1.06427119856242</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>16.135</t>
+          <t>1.228578310817</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16.306</t>
+          <t>1.18814262483581</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16.559</t>
+          <t>1.13752638307827</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>16.883</t>
+          <t>1.15930153122636</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17.315</t>
+          <t>0.989495267857273</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17.717</t>
+          <t>0.877607195478178</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>17.972</t>
+          <t>0.831203997618111</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>18.029</t>
+          <t>0.570217425752171</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>18.359</t>
+          <t>0.542507934610207</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>18.796</t>
+          <t>0.49895344457737</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>0.554434054844215</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>0.671856563455826</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>19.033</t>
+          <t>0.80966804724733</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>40599.839</t>
+          <t>-0.0435366481549273</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>41143.486</t>
+          <t>-0.0150760898400104</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41054.172</t>
+          <t>0.0905158791677094</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>41827.744</t>
+          <t>0.0993363753693495</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>42189.165</t>
+          <t>0.0721890970245251</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>42680.822</t>
+          <t>0.0745381677960879</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>43115.103</t>
+          <t>0.0300504797225987</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>43564.346</t>
+          <t>-0.0115343962051527</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>44087.232</t>
+          <t>-0.217903311490246</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>44292.887</t>
+          <t>-0.16491086489782</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>44369.551</t>
+          <t>-0.169399933519943</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>45142.592</t>
+          <t>-0.182463315312327</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>45750.837</t>
+          <t>-0.163348855487318</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>45573.368</t>
+          <t>-0.161876742534886</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>44374.474</t>
+          <t>-0.094241505862075</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>26426.569</t>
+          <t>112336373281.748</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>26837.401</t>
+          <t>114170089593.495</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>109808528190.262</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>27355.531</t>
+          <t>115216684378.23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>27748.134</t>
+          <t>119589948130.09</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>28310.735</t>
+          <t>128107853749.218</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>28707.965</t>
+          <t>126819501574.663</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>29182.183</t>
+          <t>127722484637.155</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>29479.918</t>
+          <t>135015514827.961</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>29718.084</t>
+          <t>141716864184.47</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>30039.004</t>
+          <t>142945604987.336</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>30792.788</t>
+          <t>155500801594.037</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>31249.713</t>
+          <t>157492751259.794</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>31549.881</t>
+          <t>143245890847.205</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>30509.279</t>
+          <t>118807059258.08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>31832620361.4917</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>32417515580.2283</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13.12</t>
+          <t>30054180210.2987</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>31058259897.8744</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>15.12</t>
+          <t>32575222655.904</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>15.83</t>
+          <t>33608856561.9837</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>14.81</t>
+          <t>35655107015.2263</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>37974541834.1766</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>42871273042.2151</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>46209714164.7541</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>15.05</t>
+          <t>47309840498.8342</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>15.55</t>
+          <t>49537734660.0265</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>15.72</t>
+          <t>48407418024.2854</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>46890862080.2975</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>42144312417.667</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>2127885.85143704</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>2005028.04125136</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36.91</t>
+          <t>2018305.77167398</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>38.96</t>
+          <t>2075061.41095187</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>2240986.15123089</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>41.87</t>
+          <t>2509538.17766998</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>2479151.21351691</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>2358008.36759668</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>39.44</t>
+          <t>2051556.33181392</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>1876854.0349889</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>46.82</t>
+          <t>1804604.07297134</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>1838352.89893922</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>1611014.4586664</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>46.22</t>
+          <t>1315937.26140791</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>47.37</t>
+          <t>1323831.27913801</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>55.46</t>
+          <t>170786.328369199</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.77</t>
+          <t>173903.506288731</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>49.97</t>
+          <t>175187.322777866</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>180121.473741634</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>189748.486745507</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>191669.462382245</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>44.04</t>
+          <t>182917.032849518</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>42.93</t>
+          <t>187310.823919342</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>205358.688726894</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>225958.974085414</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>38.12</t>
+          <t>247634.588596055</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>36.77</t>
+          <t>265744.576682516</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>304375.154844382</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>36.08</t>
+          <t>339973.071649516</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>302562.368912875</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>490028.035257268</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.01</t>
+          <t>496506.103386738</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.76</t>
+          <t>469666.080097466</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21.46</t>
+          <t>486723.469334024</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22.84</t>
+          <t>521232.788690617</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>561543.025265601</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>23.92</t>
+          <t>536248.174714343</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24.84</t>
+          <t>547009.298419486</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>619102.055497315</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>704807.995828407</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>756179.010400663</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>856146.304847407</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>28.97</t>
+          <t>972065.694908132</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>965826.079785142</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>740411.622442741</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>0.691219282159373</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.12</t>
+          <t>0.726082414457233</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>0.912686357530926</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>0.932818835288297</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>0.921378372879522</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>51.72</t>
+          <t>0.933743778831401</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>0.835458282262771</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>0.770114109640439</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>0.615481999462696</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>52.98</t>
+          <t>0.520576787664462</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>52.07</t>
+          <t>0.54290680290115</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>51.73</t>
+          <t>0.529935262807366</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>51.24</t>
+          <t>0.614231951002822</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>0.734151424680189</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>51.18</t>
+          <t>0.872677433279726</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>533987.2251955</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>585797.963056151</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>553845.317462387</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>560042.866636669</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>544779.997723464</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>25.29</t>
+          <t>490862.299620708</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>487753.870096426</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25.66</t>
+          <t>535445.917174024</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>24.08</t>
+          <t>650426.752640543</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>23.02</t>
+          <t>733498.959257805</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>21.66</t>
+          <t>753665.752208157</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>784118.463098888</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>894269.069094088</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>18.31</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.840781231385862</t>
+          <t>1994.7125582913</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.796666774552586</t>
+          <t>2019.61931932169</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.878518444762489</t>
+          <t>1862.66998514402</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.895479663178239</t>
+          <t>1904.67855355748</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262380506083</t>
+          <t>1967.22161096105</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271976951272</t>
+          <t>1990.70400002273</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987056528</t>
+          <t>2059.22719380104</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752963977825</t>
+          <t>2143.3715166153</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017009933639</t>
+          <t>2385.50118198798</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923184260651</t>
+          <t>2563.04850823964</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793929556715</t>
+          <t>2576.87290972658</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796432001820435</t>
+          <t>2635.51859737747</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660730035597</t>
+          <t>2531.75548372055</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902071681034</t>
+          <t>2430.82524612612</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948696375644</t>
+          <t>2214.24095756737</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>46052213082.7399</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>50226116403.7203</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>41695709486.3919</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>44470935130.2202</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>43119827493.5933</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>44797894563.6602</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>49713434449.494</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>51651132522.7185</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.607</t>
+          <t>58280086002.6545</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>65528463186.9557</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>62191579386.3525</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.764</t>
+          <t>63809700494.4503</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>64790215705.4714</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>66765440230.6631</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>55114075349.0068</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>45536412039.6929</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>49288027155.9417</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>40782810509.6391</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>44981196891.3573</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>43938269041.2912</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>45452260127.1318</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>50060683910.1827</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>52395235160.9828</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>58936864712.8174</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>65258089512.8545</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.029</t>
+          <t>62556420169.0894</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>64447596922.9318</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.221</t>
+          <t>66385199801.0624</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>68444414945.9872</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.296</t>
+          <t>56044252748.2578</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.926</t>
+          <t>515801043.046977</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.313</t>
+          <t>938089247.778568</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4.051</t>
+          <t>912898976.752876</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4.085</t>
+          <t>-510261761.137118</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.956</t>
+          <t>-818441547.697941</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.539</t>
+          <t>-654365563.471672</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.533</t>
+          <t>-347249460.688643</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.901</t>
+          <t>-744102638.264282</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.834</t>
+          <t>-656778710.162916</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>270373674.101203</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5.693</t>
+          <t>-364840782.736891</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>5.919</t>
+          <t>-637896428.481533</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6.729</t>
+          <t>-1594984095.59098</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1678974715.32402</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-930177399.250991</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.105</t>
+          <t>3373.49634094769</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.325</t>
+          <t>3486.02939097926</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.224</t>
+          <t>3562.70346916729</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.279</t>
+          <t>3681.39858348558</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.274</t>
+          <t>3779.77705796177</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.138</t>
+          <t>3849.51147553874</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.183</t>
+          <t>3779.62560792285</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.378</t>
+          <t>3794.01216376217</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2.927</t>
+          <t>3853.73421919856</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.358</t>
+          <t>3897.31206728722</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3.474</t>
+          <t>3975.87474262883</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3.683</t>
+          <t>4032.17283791241</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.213</t>
+          <t>4086.84059394832</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4.619</t>
+          <t>4215.41906371819</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.021</t>
+          <t>4146.5590730801</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.015</t>
+          <t>3656.10752376814</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>3768.76950343286</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>3848.16199296806</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.089</t>
+          <t>3983.89859658804</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.072</t>
+          <t>4094.46281233179</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>4149.85330071568</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>4077.36064278548</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.102</t>
+          <t>4101.7165197373</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.362</t>
+          <t>4172.98652961713</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>4198.76490150255</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.598</t>
+          <t>4300.29762550216</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.663</t>
+          <t>4355.13978167441</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>4427.74513057066</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.073</t>
+          <t>4534.22710885481</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.908</t>
+          <t>4464.14588773713</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>191.08</t>
+          <t>264094.051320262</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>182.65</t>
+          <t>284159.037820871</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>202.42</t>
+          <t>273709.314934043</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>200.75</t>
+          <t>279199.718799629</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>195.98</t>
+          <t>267446.112383629</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>182.29</t>
+          <t>271816.639549609</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>185.87</t>
+          <t>278622.926817104</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>181.42</t>
+          <t>289676.973552407</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>170.99</t>
+          <t>341425.323118483</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>143.46</t>
+          <t>405297.403200335</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>151.99</t>
+          <t>428302.320226843</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>153.91</t>
+          <t>481657.008501385</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>176.32</t>
+          <t>574777.868225327</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>196.6</t>
+          <t>620446.232596912</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>215.65</t>
+          <t>467638.55616313</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>108.61</t>
+          <t>19503791424.1916</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>106.43</t>
+          <t>19537127116.6811</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>122.86</t>
+          <t>18794186905.0984</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>118.81</t>
+          <t>19892547073.0987</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>113.75</t>
+          <t>19999490259.0613</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>115.93</t>
+          <t>23325894040.6939</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>98.95</t>
+          <t>23548977298.3232</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>87.76</t>
+          <t>23242255365.7498</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>83.12</t>
+          <t>24203706983.4116</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>57.02</t>
+          <t>26328366411.9215</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>54.25</t>
+          <t>27118947440.468</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>30934402342.3498</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>55.44</t>
+          <t>32750788740.1019</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>67.19</t>
+          <t>29249008942.2321</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>80.97</t>
+          <t>21054379945.9726</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>228255.448858</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>232407.002732804</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>232698.198545268</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>245836.958654195</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>248998.501493306</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>265066.114677891</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>266618.694809451</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>280372.844760904</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-21.79</t>
+          <t>334460.20865113</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>395652.878511208</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>429718.544386225</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-18.25</t>
+          <t>496999.274809229</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>577897.951572278</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-16.19</t>
+          <t>633477.962188218</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>476147.312084785</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>79853.776</t>
+          <t>55249630998.2806</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>82784.791</t>
+          <t>55197148845.9636</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84793.095</t>
+          <t>49753780777.6843</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>88652.102</t>
+          <t>55068485389.8311</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>92100.437</t>
+          <t>57781868790.6679</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>95156.551</t>
+          <t>66128163787.1751</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>95382.128</t>
+          <t>69502791819.0436</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>97592.551</t>
+          <t>71984534528.5106</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>100775.955</t>
+          <t>80421474578.9252</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>101845.661</t>
+          <t>89209148303.2666</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>104909.201</t>
+          <t>89672629948.318</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>108330.182</t>
+          <t>98349252501.5538</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>111525.602</t>
+          <t>98191906609.1888</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>114614.994</t>
+          <t>98473320604.8018</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>111955.464</t>
+          <t>77958797935.0074</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>53835.941</t>
+          <t>35838.6024622619</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>55955.304</t>
+          <t>51752.035088067</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>57484.22</t>
+          <t>41011.1163887754</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60029.99</t>
+          <t>33362.7601454339</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>62589.328</t>
+          <t>18447.6108903229</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>64990.917</t>
+          <t>6750.52487171849</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>65443.461</t>
+          <t>12004.232007653</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>67219.272</t>
+          <t>9304.12879150281</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>69257.77</t>
+          <t>6965.1144673525</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>70265.419</t>
+          <t>9644.52468912682</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>72994.675</t>
+          <t>-1416.22415938166</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>75789.527</t>
+          <t>-15342.2663078439</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>78140.801</t>
+          <t>-3120.08334695161</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>81315.855</t>
+          <t>-13031.7295913069</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>78922.703</t>
+          <t>-8508.7559216558</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>112336.373</t>
+          <t>-35745839574.0891</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>114170.09</t>
+          <t>-35660021729.2825</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>109808.528</t>
+          <t>-30959593872.5859</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>115216.684</t>
+          <t>-35175938316.7323</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>119589.948</t>
+          <t>-37782378531.6066</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>128107.854</t>
+          <t>-42802269746.4812</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>126819.502</t>
+          <t>-45953814520.7204</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>127722.485</t>
+          <t>-48742279162.7608</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>135015.515</t>
+          <t>-56217767595.5135</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>141716.864</t>
+          <t>-62880781891.3451</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>142945.605</t>
+          <t>-62553682507.85</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>155500.802</t>
+          <t>-67414850159.204</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>157492.751</t>
+          <t>-65441117869.0869</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>143245.891</t>
+          <t>-69224311662.5698</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>118807.059</t>
+          <t>-56904417989.0348</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>481645.38184</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>537495.33571</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>505213.28784</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>511530.97657</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>492188.79518</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.562</t>
+          <t>445777.23828</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>451330.4098</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>491428.51881</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>598035.25537</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>681849.93883</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>695307.47941</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.856</t>
+          <t>728001.0722</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.972</t>
+          <t>831977.77466</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.966</t>
+          <t>900160.78119</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>799653.89402</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>39151.876</t>
+          <t>-0.0505537682835945</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>39988.59</t>
+          <t>-0.0477383459926155</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>40959.019</t>
+          <t>-0.0491216489491948</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>42638.172</t>
+          <t>-0.0426597618112985</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>43535.273</t>
+          <t>-0.0422333984935077</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>43726.593</t>
+          <t>-0.0377707762574282</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>43258.79</t>
+          <t>-0.0334385502853877</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>43735.644</t>
+          <t>-0.0342398104056621</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>44785.2</t>
+          <t>-0.0333821394006145</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>45433.93</t>
+          <t>-0.0299482616048739</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>46812.032</t>
+          <t>-0.0324916953700324</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>48266.861</t>
+          <t>-0.0335218444260043</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>49314.445</t>
+          <t>-0.0327458482190856</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>50422.893</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>48549.407</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>465340.671482329</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>521488.798651422</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>496303.293015968</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>483449.282630376</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>477855.563537439</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>431683.994937708</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>441795.012050519</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>487938.915002717</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>606583.421349111</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>690968.940876866</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.248</t>
+          <t>724059.701269968</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.266</t>
+          <t>764489.446355203</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>867055.557783028</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>967793.77757274</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>912973.106233138</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>31832.62</t>
+          <t>679733.554643271</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>32417.516</t>
+          <t>758441.257490796</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>30054.18</t>
+          <t>717904.276715278</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>31058.26</t>
+          <t>703585.461813047</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>32575.223</t>
+          <t>693857.950583344</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>33608.857</t>
+          <t>625554.88267815</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>35655.107</t>
+          <t>636125.742097246</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>37974.542</t>
+          <t>700131.441621817</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>42871.273</t>
+          <t>872621.151126705</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>46209.714</t>
+          <t>988910.628243449</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>47309.84</t>
+          <t>1029297.71456805</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>49537.735</t>
+          <t>1077681.83988703</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>48407.418</t>
+          <t>1221323.84656418</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>46890.862</t>
+          <t>1365623.42467672</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>42144.312</t>
+          <t>1295764.70313376</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>69.12</t>
+          <t>3926439.23683898</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>4312841.93526092</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>91.27</t>
+          <t>4051046.55166359</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>93.28</t>
+          <t>4085394.52495392</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>92.14</t>
+          <t>3956020.15316128</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>93.37</t>
+          <t>3539065.09857788</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>83.55</t>
+          <t>3533085.32234121</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.01</t>
+          <t>3900647.95463223</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>61.55</t>
+          <t>4834248.85836636</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>52.06</t>
+          <t>5510229.03828239</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>54.29</t>
+          <t>5693345.01691844</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>52.99</t>
+          <t>5918710.30586855</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>61.42</t>
+          <t>6729429.19981627</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>73.42</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>87.27</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.128</t>
+          <t>679733.554643271</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.005</t>
+          <t>684865.116035224</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>701696.991021963</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.075</t>
+          <t>684893.370012139</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>695002.998970758</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>709862.782248644</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.479</t>
+          <t>716801.079457236</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.358</t>
+          <t>724230.600223024</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.052</t>
+          <t>727772.272550221</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.877</t>
+          <t>736509.319033262</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>755398.524855962</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.838</t>
+          <t>775456.249202919</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>784326.25792096</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.316</t>
+          <t>793857.456750158</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.324</t>
+          <t>771062.532633701</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>465340.671482329</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>470500.676099497</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>483677.566638523</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>467597.759430376</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>475807.863984618</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>486782.646277826</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>494757.91598442</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>502468.140800356</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>504035.435613977</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>512125.580951395</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>528054.878442189</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>546208.501622052</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>552725.117295964</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>558479.781745749</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>539168.337124448</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>335490.925836729</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>379910.022539204</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>354851.230874722</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>385760.909296953</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>377703.822146656</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>357189.06362185</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>369612.618882754</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>401888.470748183</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>489049.183353295</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>568477.178516551</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>568679.320281951</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>585712.377022974</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>673908.201915822</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>706935.604343281</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>611939.406586245</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>53835941357.0138</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>55955303563.4254</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>57484220475.0143</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>60029989721.8908</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>62589328302.789</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>64990917290.373</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>65443461476.0625</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>67219272307.8071</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>69257769893.7489</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>70265418723.5347</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>72994674749.8197</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>75789527095.9692</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>78140800840.3513</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>81315855281.0302</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>78922702805.6555</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>79853775648.1248</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>82784790912.4061</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>84793095066.4534</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>88652101910.435</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>92100437054.3101</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>95156551170.7407</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>95382128007.0405</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>97592551325.7616</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>100775955495.642</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>101845661327.336</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>104909200812.226</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>108330182443.347</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>111525601574.301</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>114614993813.482</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>111955464328.865</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>39151875718.7615</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>39988589784.0459</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>40959019369.3306</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>42638171975.2026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>43535272876.1799</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>43726593244.4663</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>43258789548.0469</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>43735643798.9918</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>44785199526.7311</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>45433930135.9473</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>46812032066.1867</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>48266861001.9457</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>49314445312.3592</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>50422893450.2674</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>48549407117.7642</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>21841200</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>21966000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>22034700</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>22252600</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>22493900</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>22930100</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>23393105.5806433</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>23793100</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>24149600</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>24256100</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>24395800</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>24874100</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>25187900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>25277735.5571035</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>25078809.506742</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>15958500</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>16051300</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>16135000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>16306300</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>16559000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>16882900</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>17314800</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>17717200</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>17971600</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>18029200</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>18359400</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>18796200</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>19120100</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>19290100</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>19033300</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>40599839200</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>41143485600</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>41054172200</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>41827743700</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>42189165000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>42680822000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>43115102911.5583</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>43564346300</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>44087231700</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>44292887500</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>44369551000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>45142592300</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>45750836700</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>45573368085.9512</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>44374474453.1903</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>26426568700</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>26837401000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>26858999500</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>27355530800</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>27748134200</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>28310734600</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>28707965400</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>29182183200</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>29479918000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>29718083900</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>30039004500</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>30792788300</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>31249713300</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>31549881000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>30509279400</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.115064863872481</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.122824041380863</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.131178552927775</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.139855419341338</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.151165718831045</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.158276403090031</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.148063865432393</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.148378488449053</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.138874929593949</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.141980402819401</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.150523193471181</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.155456241362467</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.157207962015697</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.176976462989848</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.171778646838757</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.330346728312496</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.34945440899313</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.369075878158331</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.389581381411308</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.396906296214269</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.418701443239057</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.411514557796667</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.422333833744622</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.39435686951909</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.463301239446308</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.468235395421219</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.476813202042057</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.479029026662959</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.462192916504095</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.473675289854856</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.554588407815023</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.527721549626007</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.499745568913894</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.470563199247354</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.451927984954686</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.423022153670912</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.44042157677094</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.429287677806325</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.466768200886961</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.39471835773429</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.3812414111076</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.367730556595476</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.363763011321344</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.360830620506057</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.354546063306387</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.192904605624275</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.200113075185827</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.20758879667445</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.214562578033492</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.228392612827319</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.229868284167139</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.239162143213746</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.248423464470472</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.257216912637063</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.239965130230706</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.262704438874699</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.278571249243567</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.28967845123482</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.314434245991452</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.305133464974963</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.472036348240102</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.481218432167405</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.489860173111289</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.497641148403368</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.498564435935901</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.517194075933086</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.495523369331111</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.495023115143772</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.501993812675581</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.529835336487165</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.520685151282691</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.51730304551646</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.512367965452671</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.498914654158309</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.511788009305094</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.335059046135623</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.318668492646768</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.302551030214261</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.28779627356314</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.27304295123678</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.252937639899775</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.265314487455142</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.256553420385756</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.240789274687356</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.23019953328213</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.21661040984261</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.204125705239973</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.197953583312509</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.186651099850238</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.183078525719943</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2104988.71341</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2324819.29448</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2224223.78423</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2278989.53668</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2273650.16017</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2137660.35747</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2182848.1148</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2378133.78076</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>2927417.2305</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>3357865.69895</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>3474255.19799</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>3682927.63676</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>4212757.68836</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>4618580.06788</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4020984.88656</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1015224.48048</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1138351.28003</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1072755.50759</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1089346.37111</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1071561.77273</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>982743.9463</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1005738.36098</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1102019.91237</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1361670.33448</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1557387.80676</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1597977.03485</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1663394.21691</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1895232.04848</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2072559.02902</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1907704.10972</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3301276.40726932</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3359351.1456276</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3418930.21646495</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3485263.46500361</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3558016.62368352</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>3643776.52409036</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>3730129.56765716</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>3817527.93087565</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3893438.56161742</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3975552.41871637</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>4059826.08095388</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>4150495.72163218</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>4239740.68000487</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
